--- a/data/ALLE_zeitreihe.xlsx
+++ b/data/ALLE_zeitreihe.xlsx
@@ -2738,13 +2738,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E88BBA50-01BA-4422-9129-C2DC441EEBCC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C38DEA-53A5-4F24-A9D5-CBF6BD5352CF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4B1CBAF-2105-462E-A162-A9BF5127487A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BBF0B88-B203-4672-A21E-5CCD77D8AC98}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9672CD4D-0233-4CC8-99C2-157CCECCB21F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D4A594F-8E98-4554-A566-071BD827686A}"/>
 </file>
--- a/data/ALLE_zeitreihe.xlsx
+++ b/data/ALLE_zeitreihe.xlsx
@@ -595,7 +595,7 @@
         <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>30.2403846153846</v>
+        <v>30.5</v>
       </c>
       <c r="E12" t="n">
         <v>59</v>
@@ -1372,7 +1372,7 @@
         <v>17</v>
       </c>
       <c r="C51" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D51" t="n">
         <v>35.4014598540146</v>
@@ -1381,7 +1381,7 @@
         <v>105</v>
       </c>
       <c r="F51" t="n">
-        <v>23.3576642335766</v>
+        <v>24.4604316546763</v>
       </c>
     </row>
     <row r="52">
@@ -1392,7 +1392,7 @@
         <v>17</v>
       </c>
       <c r="C52" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D52" t="n">
         <v>31.530612244898</v>
@@ -1401,7 +1401,7 @@
         <v>129</v>
       </c>
       <c r="F52" t="n">
-        <v>13.4228187919463</v>
+        <v>12.8378378378378</v>
       </c>
     </row>
     <row r="53">
@@ -1412,7 +1412,7 @@
         <v>17</v>
       </c>
       <c r="C53" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D53" t="n">
         <v>30.4428571428571</v>
@@ -1421,7 +1421,7 @@
         <v>40</v>
       </c>
       <c r="F53" t="n">
-        <v>44.4444444444444</v>
+        <v>42.8571428571429</v>
       </c>
     </row>
     <row r="54">
@@ -1512,7 +1512,7 @@
         <v>17</v>
       </c>
       <c r="C58" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D58" t="n">
         <v>30.3974358974359</v>
@@ -1521,7 +1521,7 @@
         <v>51</v>
       </c>
       <c r="F58" t="n">
-        <v>35.4430379746835</v>
+        <v>34.6153846153846</v>
       </c>
     </row>
     <row r="59">
@@ -2502,6 +2502,24 @@
       </c>
       <c r="F107" t="n">
         <v>14.2857142857143</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1"/>
+      <c r="B108" t="n">
+        <v>17</v>
+      </c>
+      <c r="C108" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2738,13 +2756,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C38DEA-53A5-4F24-A9D5-CBF6BD5352CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0160486-45DB-4031-80F9-29819676096E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BBF0B88-B203-4672-A21E-5CCD77D8AC98}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02A775A5-43F3-41A5-BEC7-6F548D89BD71}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D4A594F-8E98-4554-A566-071BD827686A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAE1BE16-09F8-440A-967F-02C62647F1C5}"/>
 </file>
--- a/data/ALLE_zeitreihe.xlsx
+++ b/data/ALLE_zeitreihe.xlsx
@@ -635,13 +635,13 @@
         <v>131</v>
       </c>
       <c r="D14" t="n">
-        <v>33.1472868217054</v>
+        <v>33.1908396946565</v>
       </c>
       <c r="E14" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F14" t="n">
-        <v>32.824427480916</v>
+        <v>31.2977099236641</v>
       </c>
     </row>
     <row r="15">
@@ -655,7 +655,7 @@
         <v>119</v>
       </c>
       <c r="D15" t="n">
-        <v>32.7881355932203</v>
+        <v>32.7058823529412</v>
       </c>
       <c r="E15" t="n">
         <v>86</v>
@@ -975,7 +975,7 @@
         <v>127</v>
       </c>
       <c r="D31" t="n">
-        <v>30.5238095238095</v>
+        <v>30.496062992126</v>
       </c>
       <c r="E31" t="n">
         <v>77</v>
@@ -1175,7 +1175,7 @@
         <v>197</v>
       </c>
       <c r="D41" t="n">
-        <v>24.4744897959184</v>
+        <v>24.4467005076142</v>
       </c>
       <c r="E41" t="n">
         <v>44</v>
@@ -1215,7 +1215,7 @@
         <v>66</v>
       </c>
       <c r="D43" t="n">
-        <v>29.9230769230769</v>
+        <v>29.469696969697</v>
       </c>
       <c r="E43" t="n">
         <v>35</v>
@@ -1375,13 +1375,13 @@
         <v>139</v>
       </c>
       <c r="D51" t="n">
-        <v>35.4014598540146</v>
+        <v>35.3956834532374</v>
       </c>
       <c r="E51" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F51" t="n">
-        <v>24.4604316546763</v>
+        <v>23.021582733813</v>
       </c>
     </row>
     <row r="52">
@@ -1392,16 +1392,16 @@
         <v>17</v>
       </c>
       <c r="C52" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D52" t="n">
-        <v>31.530612244898</v>
+        <v>31.4362416107383</v>
       </c>
       <c r="E52" t="n">
         <v>129</v>
       </c>
       <c r="F52" t="n">
-        <v>12.8378378378378</v>
+        <v>13.4228187919463</v>
       </c>
     </row>
     <row r="53">
@@ -1492,16 +1492,16 @@
         <v>17</v>
       </c>
       <c r="C57" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D57" t="n">
-        <v>28.8229166666667</v>
+        <v>28.8041237113402</v>
       </c>
       <c r="E57" t="n">
         <v>36</v>
       </c>
       <c r="F57" t="n">
-        <v>62.5</v>
+        <v>62.8865979381443</v>
       </c>
     </row>
     <row r="58">
@@ -2472,7 +2472,7 @@
         <v>18</v>
       </c>
       <c r="C106" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D106" t="n">
         <v>39.0526315789474</v>
@@ -2481,7 +2481,7 @@
         <v>141</v>
       </c>
       <c r="F106" t="n">
-        <v>17.5438596491228</v>
+        <v>18.0232558139535</v>
       </c>
     </row>
     <row r="107">
@@ -2502,24 +2502,6 @@
       </c>
       <c r="F107" t="n">
         <v>14.2857142857143</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="1"/>
-      <c r="B108" t="n">
-        <v>17</v>
-      </c>
-      <c r="C108" t="n">
-        <v>2</v>
-      </c>
-      <c r="D108" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="E108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" t="n">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2756,13 +2738,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0160486-45DB-4031-80F9-29819676096E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36D96DD2-B88A-43D5-A2E4-012FA4E0860C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02A775A5-43F3-41A5-BEC7-6F548D89BD71}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2D044EB-FC5D-4C22-8FA8-2BC1A8D0C1EE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAE1BE16-09F8-440A-967F-02C62647F1C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86AB3EF7-48EC-458E-B43E-AB47248920D1}"/>
 </file>
--- a/data/ALLE_zeitreihe.xlsx
+++ b/data/ALLE_zeitreihe.xlsx
@@ -392,16 +392,16 @@
         <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>32.0689655172414</v>
+        <v>32.9736842105263</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F2" t="n">
-        <v>34.4827586206897</v>
+        <v>28.9473684210526</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D3" t="n">
-        <v>32.2913385826772</v>
+        <v>31.983606557377</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F3" t="n">
-        <v>38.5826771653543</v>
+        <v>36.8852459016393</v>
       </c>
     </row>
     <row r="4">
@@ -432,16 +432,16 @@
         <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D4" t="n">
-        <v>33.0510204081633</v>
+        <v>33.4949494949495</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
-        <v>24.4897959183673</v>
+        <v>28.2828282828283</v>
       </c>
     </row>
     <row r="5">
@@ -452,16 +452,16 @@
         <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D5" t="n">
-        <v>32.6271186440678</v>
+        <v>32.7079646017699</v>
       </c>
       <c r="E5" t="n">
         <v>85</v>
       </c>
       <c r="F5" t="n">
-        <v>27.9661016949153</v>
+        <v>24.7787610619469</v>
       </c>
     </row>
     <row r="6">
@@ -472,16 +472,16 @@
         <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="D6" t="n">
-        <v>32.6574074074074</v>
+        <v>33.4883720930233</v>
       </c>
       <c r="E6" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="F6" t="n">
-        <v>22.2222222222222</v>
+        <v>20.9302325581395</v>
       </c>
     </row>
     <row r="7">
@@ -492,16 +492,16 @@
         <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="D7" t="n">
-        <v>30.5833333333333</v>
+        <v>33.9462365591398</v>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F7" t="n">
-        <v>46.2962962962963</v>
+        <v>34.4086021505376</v>
       </c>
     </row>
     <row r="8">
@@ -512,16 +512,16 @@
         <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D8" t="n">
-        <v>32.7530864197531</v>
+        <v>33.2597402597403</v>
       </c>
       <c r="E8" t="n">
         <v>54</v>
       </c>
       <c r="F8" t="n">
-        <v>33.3333333333333</v>
+        <v>29.8701298701299</v>
       </c>
     </row>
     <row r="9">
@@ -532,16 +532,16 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D9" t="n">
-        <v>31.2142857142857</v>
+        <v>31.5</v>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F9" t="n">
-        <v>29.5918367346939</v>
+        <v>25.9615384615385</v>
       </c>
     </row>
     <row r="10">
@@ -552,16 +552,16 @@
         <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D10" t="n">
-        <v>28.515625</v>
+        <v>29.031746031746</v>
       </c>
       <c r="E10" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F10" t="n">
-        <v>54.6875</v>
+        <v>49.2063492063492</v>
       </c>
     </row>
     <row r="11">
@@ -572,16 +572,16 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D11" t="n">
-        <v>30.1529411764706</v>
+        <v>30.0116279069767</v>
       </c>
       <c r="E11" t="n">
         <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>41.1764705882353</v>
+        <v>41.8604651162791</v>
       </c>
     </row>
     <row r="12">
@@ -592,16 +592,16 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>30.5</v>
+        <v>31.6862745098039</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F12" t="n">
-        <v>43.2692307692308</v>
+        <v>36.2745098039216</v>
       </c>
     </row>
     <row r="13">
@@ -615,13 +615,13 @@
         <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>33.3636363636364</v>
+        <v>35.0649350649351</v>
       </c>
       <c r="E13" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F13" t="n">
-        <v>33.7662337662338</v>
+        <v>22.0779220779221</v>
       </c>
     </row>
     <row r="14">
@@ -632,16 +632,16 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D14" t="n">
-        <v>33.1908396946565</v>
+        <v>34.6818181818182</v>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F14" t="n">
-        <v>31.2977099236641</v>
+        <v>28.7878787878788</v>
       </c>
     </row>
     <row r="15">
@@ -652,16 +652,16 @@
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D15" t="n">
-        <v>32.7058823529412</v>
+        <v>31.5689655172414</v>
       </c>
       <c r="E15" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F15" t="n">
-        <v>27.7310924369748</v>
+        <v>27.5862068965517</v>
       </c>
     </row>
     <row r="16">
@@ -672,16 +672,16 @@
         <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>30.0655737704918</v>
+        <v>29.1896551724138</v>
       </c>
       <c r="E16" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F16" t="n">
-        <v>45.9016393442623</v>
+        <v>48.2758620689655</v>
       </c>
     </row>
     <row r="17">
@@ -692,16 +692,16 @@
         <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D17" t="n">
-        <v>32.4927536231884</v>
+        <v>32.8759124087591</v>
       </c>
       <c r="E17" t="n">
         <v>105</v>
       </c>
       <c r="F17" t="n">
-        <v>23.9130434782609</v>
+        <v>23.3576642335766</v>
       </c>
     </row>
     <row r="18">
@@ -712,16 +712,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>32.5826086956522</v>
+        <v>31.5948275862069</v>
       </c>
       <c r="E18" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F18" t="n">
-        <v>15.6521739130435</v>
+        <v>20.6896551724138</v>
       </c>
     </row>
     <row r="19">
@@ -732,16 +732,16 @@
         <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D19" t="n">
-        <v>35.0403225806452</v>
+        <v>34.5609756097561</v>
       </c>
       <c r="E19" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F19" t="n">
-        <v>33.8709677419355</v>
+        <v>35.7723577235772</v>
       </c>
     </row>
     <row r="20">
@@ -755,13 +755,13 @@
         <v>85</v>
       </c>
       <c r="D20" t="n">
-        <v>32.1411764705882</v>
+        <v>31.0117647058824</v>
       </c>
       <c r="E20" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F20" t="n">
-        <v>25.8823529411765</v>
+        <v>35.2941176470588</v>
       </c>
     </row>
     <row r="21">
@@ -772,16 +772,16 @@
         <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D21" t="n">
-        <v>29.4621212121212</v>
+        <v>29.9347826086956</v>
       </c>
       <c r="E21" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="F21" t="n">
-        <v>53.7878787878788</v>
+        <v>47.8260869565217</v>
       </c>
     </row>
     <row r="22">
@@ -792,16 +792,16 @@
         <v>17</v>
       </c>
       <c r="C22" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D22" t="n">
-        <v>29.4152542372881</v>
+        <v>30.6724137931035</v>
       </c>
       <c r="E22" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F22" t="n">
-        <v>46.6101694915254</v>
+        <v>42.2413793103448</v>
       </c>
     </row>
     <row r="23">
@@ -812,16 +812,16 @@
         <v>17</v>
       </c>
       <c r="C23" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D23" t="n">
-        <v>31.1769911504425</v>
+        <v>31.4220183486239</v>
       </c>
       <c r="E23" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="F23" t="n">
-        <v>46.0176991150443</v>
+        <v>33.9449541284404</v>
       </c>
     </row>
     <row r="24">
@@ -832,16 +832,16 @@
         <v>17</v>
       </c>
       <c r="C24" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D24" t="n">
-        <v>27.4345238095238</v>
+        <v>26.4597701149425</v>
       </c>
       <c r="E24" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F24" t="n">
-        <v>69.047619047619</v>
+        <v>72.9885057471264</v>
       </c>
     </row>
     <row r="25">
@@ -852,16 +852,16 @@
         <v>17</v>
       </c>
       <c r="C25" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D25" t="n">
-        <v>26.6242424242424</v>
+        <v>26.3765432098765</v>
       </c>
       <c r="E25" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F25" t="n">
-        <v>63.030303030303</v>
+        <v>57.4074074074074</v>
       </c>
     </row>
     <row r="26">
@@ -872,16 +872,16 @@
         <v>17</v>
       </c>
       <c r="C26" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D26" t="n">
-        <v>30.9</v>
+        <v>31.7864077669903</v>
       </c>
       <c r="E26" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F26" t="n">
-        <v>41</v>
+        <v>38.8349514563107</v>
       </c>
     </row>
     <row r="27">
@@ -892,16 +892,16 @@
         <v>17</v>
       </c>
       <c r="C27" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D27" t="n">
-        <v>29.7175572519084</v>
+        <v>29.8897637795276</v>
       </c>
       <c r="E27" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F27" t="n">
-        <v>50.381679389313</v>
+        <v>54.3307086614173</v>
       </c>
     </row>
     <row r="28">
@@ -912,16 +912,16 @@
         <v>17</v>
       </c>
       <c r="C28" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D28" t="n">
-        <v>29.9901960784314</v>
+        <v>30</v>
       </c>
       <c r="E28" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F28" t="n">
-        <v>56.8627450980392</v>
+        <v>56.7307692307692</v>
       </c>
     </row>
     <row r="29">
@@ -932,16 +932,16 @@
         <v>17</v>
       </c>
       <c r="C29" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D29" t="n">
-        <v>29.8736842105263</v>
+        <v>29.247311827957</v>
       </c>
       <c r="E29" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F29" t="n">
-        <v>50.5263157894737</v>
+        <v>52.6881720430108</v>
       </c>
     </row>
     <row r="30">
@@ -952,16 +952,16 @@
         <v>17</v>
       </c>
       <c r="C30" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D30" t="n">
-        <v>30.9661016949153</v>
+        <v>31.3064516129032</v>
       </c>
       <c r="E30" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F30" t="n">
-        <v>40.6779661016949</v>
+        <v>45.1612903225806</v>
       </c>
     </row>
     <row r="31">
@@ -972,16 +972,16 @@
         <v>17</v>
       </c>
       <c r="C31" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D31" t="n">
-        <v>30.496062992126</v>
+        <v>31.3515625</v>
       </c>
       <c r="E31" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F31" t="n">
-        <v>39.3700787401575</v>
+        <v>35.15625</v>
       </c>
     </row>
     <row r="32">
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C32" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D32" t="n">
-        <v>30.3536585365854</v>
+        <v>30.3815789473684</v>
       </c>
       <c r="E32" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F32" t="n">
-        <v>41.4634146341463</v>
+        <v>40.7894736842105</v>
       </c>
     </row>
     <row r="33">
@@ -1012,16 +1012,16 @@
         <v>17</v>
       </c>
       <c r="C33" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D33" t="n">
-        <v>29.8717948717949</v>
+        <v>30.0506329113924</v>
       </c>
       <c r="E33" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F33" t="n">
-        <v>46.1538461538462</v>
+        <v>43.0379746835443</v>
       </c>
     </row>
     <row r="34">
@@ -1032,16 +1032,16 @@
         <v>17</v>
       </c>
       <c r="C34" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D34" t="n">
-        <v>33.1639344262295</v>
+        <v>33.3</v>
       </c>
       <c r="E34" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F34" t="n">
-        <v>40.983606557377</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35">
@@ -1055,13 +1055,13 @@
         <v>49</v>
       </c>
       <c r="D35" t="n">
-        <v>27.7959183673469</v>
+        <v>26.7755102040816</v>
       </c>
       <c r="E35" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F35" t="n">
-        <v>63.265306122449</v>
+        <v>67.3469387755102</v>
       </c>
     </row>
     <row r="36">
@@ -1072,16 +1072,16 @@
         <v>17</v>
       </c>
       <c r="C36" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D36" t="n">
-        <v>32.1477272727273</v>
+        <v>32.685393258427</v>
       </c>
       <c r="E36" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F36" t="n">
-        <v>25</v>
+        <v>24.7191011235955</v>
       </c>
     </row>
     <row r="37">
@@ -1095,13 +1095,13 @@
         <v>218</v>
       </c>
       <c r="D37" t="n">
-        <v>36.0733944954128</v>
+        <v>33.9724770642202</v>
       </c>
       <c r="E37" t="n">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="F37" t="n">
-        <v>11.0091743119266</v>
+        <v>16.9724770642202</v>
       </c>
     </row>
     <row r="38">
@@ -1112,16 +1112,16 @@
         <v>17</v>
       </c>
       <c r="C38" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D38" t="n">
-        <v>41.7945205479452</v>
+        <v>42.9311926605505</v>
       </c>
       <c r="E38" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F38" t="n">
-        <v>14.6118721461187</v>
+        <v>15.1376146788991</v>
       </c>
     </row>
     <row r="39">
@@ -1135,13 +1135,13 @@
         <v>193</v>
       </c>
       <c r="D39" t="n">
-        <v>33.1554404145078</v>
+        <v>33.0310880829016</v>
       </c>
       <c r="E39" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F39" t="n">
-        <v>24.8704663212435</v>
+        <v>25.9067357512953</v>
       </c>
     </row>
     <row r="40">
@@ -1155,13 +1155,13 @@
         <v>77</v>
       </c>
       <c r="D40" t="n">
-        <v>30.3246753246753</v>
+        <v>30.2727272727273</v>
       </c>
       <c r="E40" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F40" t="n">
-        <v>45.4545454545455</v>
+        <v>44.1558441558442</v>
       </c>
     </row>
     <row r="41">
@@ -1175,13 +1175,13 @@
         <v>197</v>
       </c>
       <c r="D41" t="n">
-        <v>24.4467005076142</v>
+        <v>24.0507614213198</v>
       </c>
       <c r="E41" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F41" t="n">
-        <v>77.6649746192893</v>
+        <v>77.1573604060914</v>
       </c>
     </row>
     <row r="42">
@@ -1192,16 +1192,16 @@
         <v>17</v>
       </c>
       <c r="C42" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D42" t="n">
-        <v>29.3121387283237</v>
+        <v>28.0804597701149</v>
       </c>
       <c r="E42" t="n">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="F42" t="n">
-        <v>31.7919075144509</v>
+        <v>58.6206896551724</v>
       </c>
     </row>
     <row r="43">
@@ -1212,16 +1212,16 @@
         <v>17</v>
       </c>
       <c r="C43" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D43" t="n">
-        <v>29.469696969697</v>
+        <v>29.5230769230769</v>
       </c>
       <c r="E43" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F43" t="n">
-        <v>46.969696969697</v>
+        <v>49.2307692307692</v>
       </c>
     </row>
     <row r="44">
@@ -1235,13 +1235,13 @@
         <v>90</v>
       </c>
       <c r="D44" t="n">
-        <v>30.4222222222222</v>
+        <v>30.2555555555556</v>
       </c>
       <c r="E44" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F44" t="n">
-        <v>37.7777777777778</v>
+        <v>42.2222222222222</v>
       </c>
     </row>
     <row r="45">
@@ -1255,13 +1255,13 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>28.5625</v>
+        <v>28.3214285714286</v>
       </c>
       <c r="E45" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F45" t="n">
-        <v>47.3214285714286</v>
+        <v>48.2142857142857</v>
       </c>
     </row>
     <row r="46">
@@ -1275,13 +1275,13 @@
         <v>149</v>
       </c>
       <c r="D46" t="n">
-        <v>26.8724832214765</v>
+        <v>26.7046979865772</v>
       </c>
       <c r="E46" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F46" t="n">
-        <v>60.4026845637584</v>
+        <v>61.0738255033557</v>
       </c>
     </row>
     <row r="47">
@@ -1295,13 +1295,13 @@
         <v>196</v>
       </c>
       <c r="D47" t="n">
-        <v>34.8316326530612</v>
+        <v>34.265306122449</v>
       </c>
       <c r="E47" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F47" t="n">
-        <v>22.9591836734694</v>
+        <v>23.9795918367347</v>
       </c>
     </row>
     <row r="48">
@@ -1315,7 +1315,7 @@
         <v>64</v>
       </c>
       <c r="D48" t="n">
-        <v>30.0625</v>
+        <v>29.84375</v>
       </c>
       <c r="E48" t="n">
         <v>33</v>
@@ -1335,13 +1335,13 @@
         <v>210</v>
       </c>
       <c r="D49" t="n">
-        <v>29.8095238095238</v>
+        <v>29.4285714285714</v>
       </c>
       <c r="E49" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F49" t="n">
-        <v>58.5714285714286</v>
+        <v>62.8571428571429</v>
       </c>
     </row>
     <row r="50">
@@ -1352,16 +1352,16 @@
         <v>17</v>
       </c>
       <c r="C50" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D50" t="n">
-        <v>31.5652173913044</v>
+        <v>31.0438596491228</v>
       </c>
       <c r="E50" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F50" t="n">
-        <v>27.8260869565217</v>
+        <v>32.4561403508772</v>
       </c>
     </row>
     <row r="51">
@@ -1372,16 +1372,16 @@
         <v>17</v>
       </c>
       <c r="C51" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D51" t="n">
-        <v>35.3956834532374</v>
+        <v>35.0714285714286</v>
       </c>
       <c r="E51" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F51" t="n">
-        <v>23.021582733813</v>
+        <v>27.1428571428572</v>
       </c>
     </row>
     <row r="52">
@@ -1395,13 +1395,13 @@
         <v>149</v>
       </c>
       <c r="D52" t="n">
-        <v>31.4362416107383</v>
+        <v>30.6979865771812</v>
       </c>
       <c r="E52" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F52" t="n">
-        <v>13.4228187919463</v>
+        <v>14.7651006711409</v>
       </c>
     </row>
     <row r="53">
@@ -1415,13 +1415,13 @@
         <v>70</v>
       </c>
       <c r="D53" t="n">
-        <v>30.4428571428571</v>
+        <v>29.9714285714286</v>
       </c>
       <c r="E53" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F53" t="n">
-        <v>42.8571428571429</v>
+        <v>47.1428571428571</v>
       </c>
     </row>
     <row r="54">
@@ -1435,13 +1435,13 @@
         <v>76</v>
       </c>
       <c r="D54" t="n">
-        <v>30.1973684210526</v>
+        <v>28.421052631579</v>
       </c>
       <c r="E54" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F54" t="n">
-        <v>39.4736842105263</v>
+        <v>43.421052631579</v>
       </c>
     </row>
     <row r="55">
@@ -1455,13 +1455,13 @@
         <v>69</v>
       </c>
       <c r="D55" t="n">
-        <v>29.8550724637681</v>
+        <v>29.2753623188406</v>
       </c>
       <c r="E55" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F55" t="n">
-        <v>49.2753623188406</v>
+        <v>52.1739130434783</v>
       </c>
     </row>
     <row r="56">
@@ -1475,7 +1475,7 @@
         <v>123</v>
       </c>
       <c r="D56" t="n">
-        <v>26.5365853658537</v>
+        <v>26.0162601626016</v>
       </c>
       <c r="E56" t="n">
         <v>45</v>
@@ -1495,13 +1495,13 @@
         <v>97</v>
       </c>
       <c r="D57" t="n">
-        <v>28.8041237113402</v>
+        <v>28.6082474226804</v>
       </c>
       <c r="E57" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F57" t="n">
-        <v>62.8865979381443</v>
+        <v>64.9484536082474</v>
       </c>
     </row>
     <row r="58">
@@ -1515,13 +1515,13 @@
         <v>78</v>
       </c>
       <c r="D58" t="n">
-        <v>30.3974358974359</v>
+        <v>29.7564102564103</v>
       </c>
       <c r="E58" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F58" t="n">
-        <v>34.6153846153846</v>
+        <v>39.7435897435897</v>
       </c>
     </row>
     <row r="59">
@@ -1535,13 +1535,13 @@
         <v>69</v>
       </c>
       <c r="D59" t="n">
-        <v>30.4927536231884</v>
+        <v>30.1014492753623</v>
       </c>
       <c r="E59" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F59" t="n">
-        <v>43.4782608695652</v>
+        <v>44.9275362318841</v>
       </c>
     </row>
     <row r="60">
@@ -1555,7 +1555,7 @@
         <v>33</v>
       </c>
       <c r="D60" t="n">
-        <v>32.8181818181818</v>
+        <v>32.2424242424242</v>
       </c>
       <c r="E60" t="n">
         <v>20</v>
@@ -1595,13 +1595,13 @@
         <v>79</v>
       </c>
       <c r="D62" t="n">
-        <v>33.7215189873418</v>
+        <v>33.3670886075949</v>
       </c>
       <c r="E62" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F62" t="n">
-        <v>37.9746835443038</v>
+        <v>40.5063291139241</v>
       </c>
     </row>
     <row r="63">
@@ -1612,16 +1612,16 @@
         <v>18</v>
       </c>
       <c r="C63" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D63" t="n">
-        <v>31.225</v>
+        <v>30.9565217391304</v>
       </c>
       <c r="E63" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F63" t="n">
-        <v>38.75</v>
+        <v>40.9937888198758</v>
       </c>
     </row>
     <row r="64">
@@ -1635,13 +1635,13 @@
         <v>158</v>
       </c>
       <c r="D64" t="n">
-        <v>30.4303797468354</v>
+        <v>30.0126582278481</v>
       </c>
       <c r="E64" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F64" t="n">
-        <v>44.9367088607595</v>
+        <v>48.7341772151899</v>
       </c>
     </row>
     <row r="65">
@@ -1652,16 +1652,16 @@
         <v>18</v>
       </c>
       <c r="C65" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D65" t="n">
-        <v>31.4678899082569</v>
+        <v>31.037037037037</v>
       </c>
       <c r="E65" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="F65" t="n">
-        <v>38.5321100917431</v>
+        <v>48.1481481481482</v>
       </c>
     </row>
     <row r="66">
@@ -1675,13 +1675,13 @@
         <v>175</v>
       </c>
       <c r="D66" t="n">
-        <v>29.4685714285714</v>
+        <v>28.9371428571429</v>
       </c>
       <c r="E66" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F66" t="n">
-        <v>57.1428571428571</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67">
@@ -1695,13 +1695,13 @@
         <v>164</v>
       </c>
       <c r="D67" t="n">
-        <v>33.0243902439024</v>
+        <v>32</v>
       </c>
       <c r="E67" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="F67" t="n">
-        <v>30.4878048780488</v>
+        <v>40.8536585365854</v>
       </c>
     </row>
     <row r="68">
@@ -1715,13 +1715,13 @@
         <v>97</v>
       </c>
       <c r="D68" t="n">
-        <v>30.3298969072165</v>
+        <v>29.9484536082474</v>
       </c>
       <c r="E68" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F68" t="n">
-        <v>36.0824742268041</v>
+        <v>37.1134020618557</v>
       </c>
     </row>
     <row r="69">
@@ -1735,13 +1735,13 @@
         <v>291</v>
       </c>
       <c r="D69" t="n">
-        <v>34.7079037800687</v>
+        <v>34.2302405498282</v>
       </c>
       <c r="E69" t="n">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F69" t="n">
-        <v>32.3024054982818</v>
+        <v>34.3642611683849</v>
       </c>
     </row>
     <row r="70">
@@ -1755,13 +1755,13 @@
         <v>223</v>
       </c>
       <c r="D70" t="n">
-        <v>33.4394618834081</v>
+        <v>33.0941704035874</v>
       </c>
       <c r="E70" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F70" t="n">
-        <v>20.1793721973094</v>
+        <v>21.52466367713</v>
       </c>
     </row>
     <row r="71">
@@ -1775,13 +1775,13 @@
         <v>206</v>
       </c>
       <c r="D71" t="n">
-        <v>30.7815533980583</v>
+        <v>30.504854368932</v>
       </c>
       <c r="E71" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F71" t="n">
-        <v>37.8640776699029</v>
+        <v>38.3495145631068</v>
       </c>
     </row>
     <row r="72">
@@ -1795,13 +1795,13 @@
         <v>95</v>
       </c>
       <c r="D72" t="n">
-        <v>36.9473684210526</v>
+        <v>36.6421052631579</v>
       </c>
       <c r="E72" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F72" t="n">
-        <v>22.1052631578947</v>
+        <v>24.2105263157895</v>
       </c>
     </row>
     <row r="73">
@@ -1815,13 +1815,13 @@
         <v>137</v>
       </c>
       <c r="D73" t="n">
-        <v>34.6569343065693</v>
+        <v>34.4087591240876</v>
       </c>
       <c r="E73" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F73" t="n">
-        <v>16.0583941605839</v>
+        <v>16.7883211678832</v>
       </c>
     </row>
     <row r="74">
@@ -1832,16 +1832,16 @@
         <v>18</v>
       </c>
       <c r="C74" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D74" t="n">
-        <v>33.2941176470588</v>
+        <v>33.2280701754386</v>
       </c>
       <c r="E74" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F74" t="n">
-        <v>38.8235294117647</v>
+        <v>40.3508771929825</v>
       </c>
     </row>
     <row r="75">
@@ -1852,16 +1852,16 @@
         <v>18</v>
       </c>
       <c r="C75" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D75" t="n">
-        <v>33.0254777070064</v>
+        <v>32.4935897435897</v>
       </c>
       <c r="E75" t="n">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="F75" t="n">
-        <v>30.5732484076433</v>
+        <v>36.5384615384615</v>
       </c>
     </row>
     <row r="76">
@@ -1872,16 +1872,16 @@
         <v>18</v>
       </c>
       <c r="C76" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D76" t="n">
-        <v>35.393665158371</v>
+        <v>35.25</v>
       </c>
       <c r="E76" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F76" t="n">
-        <v>27.6018099547511</v>
+        <v>29.9107142857143</v>
       </c>
     </row>
     <row r="77">
@@ -1892,16 +1892,16 @@
         <v>18</v>
       </c>
       <c r="C77" t="n">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D77" t="n">
-        <v>30.5313653136531</v>
+        <v>30.0446096654275</v>
       </c>
       <c r="E77" t="n">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F77" t="n">
-        <v>48.7084870848708</v>
+        <v>50.185873605948</v>
       </c>
     </row>
     <row r="78">
@@ -1912,16 +1912,16 @@
         <v>18</v>
       </c>
       <c r="C78" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D78" t="n">
-        <v>32.6413043478261</v>
+        <v>32.2307692307692</v>
       </c>
       <c r="E78" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F78" t="n">
-        <v>32.6086956521739</v>
+        <v>36.2637362637363</v>
       </c>
     </row>
     <row r="79">
@@ -1935,13 +1935,13 @@
         <v>182</v>
       </c>
       <c r="D79" t="n">
-        <v>35.9945054945055</v>
+        <v>35.6153846153846</v>
       </c>
       <c r="E79" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F79" t="n">
-        <v>13.1868131868132</v>
+        <v>16.4835164835165</v>
       </c>
     </row>
     <row r="80">
@@ -1955,7 +1955,7 @@
         <v>138</v>
       </c>
       <c r="D80" t="n">
-        <v>33.8260869565217</v>
+        <v>33.5942028985507</v>
       </c>
       <c r="E80" t="n">
         <v>124</v>
@@ -1975,13 +1975,13 @@
         <v>147</v>
       </c>
       <c r="D81" t="n">
-        <v>32.3061224489796</v>
+        <v>32.7959183673469</v>
       </c>
       <c r="E81" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F81" t="n">
-        <v>18.3673469387755</v>
+        <v>19.047619047619</v>
       </c>
     </row>
     <row r="82">
@@ -1992,16 +1992,16 @@
         <v>18</v>
       </c>
       <c r="C82" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D82" t="n">
-        <v>32.5725190839695</v>
+        <v>32.0769230769231</v>
       </c>
       <c r="E82" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F82" t="n">
-        <v>32.824427480916</v>
+        <v>35.3846153846154</v>
       </c>
     </row>
     <row r="83">
@@ -2012,16 +2012,16 @@
         <v>18</v>
       </c>
       <c r="C83" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D83" t="n">
-        <v>33.1135135135135</v>
+        <v>32.7688172043011</v>
       </c>
       <c r="E83" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F83" t="n">
-        <v>26.4864864864865</v>
+        <v>29.0322580645161</v>
       </c>
     </row>
     <row r="84">
@@ -2035,13 +2035,13 @@
         <v>189</v>
       </c>
       <c r="D84" t="n">
-        <v>36.8412698412698</v>
+        <v>36.4179894179894</v>
       </c>
       <c r="E84" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F84" t="n">
-        <v>23.2804232804233</v>
+        <v>23.8095238095238</v>
       </c>
     </row>
     <row r="85">
@@ -2055,13 +2055,13 @@
         <v>110</v>
       </c>
       <c r="D85" t="n">
-        <v>37.0909090909091</v>
+        <v>36.8272727272727</v>
       </c>
       <c r="E85" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F85" t="n">
-        <v>17.2727272727273</v>
+        <v>20.9090909090909</v>
       </c>
     </row>
     <row r="86">
@@ -2075,13 +2075,13 @@
         <v>137</v>
       </c>
       <c r="D86" t="n">
-        <v>37.7153284671533</v>
+        <v>37.3065693430657</v>
       </c>
       <c r="E86" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F86" t="n">
-        <v>34.3065693430657</v>
+        <v>40.1459854014598</v>
       </c>
     </row>
     <row r="87">
@@ -2095,13 +2095,13 @@
         <v>228</v>
       </c>
       <c r="D87" t="n">
-        <v>39.2631578947368</v>
+        <v>37.6359649122807</v>
       </c>
       <c r="E87" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F87" t="n">
-        <v>32.0175438596491</v>
+        <v>34.6491228070175</v>
       </c>
     </row>
     <row r="88">
@@ -2115,13 +2115,13 @@
         <v>96</v>
       </c>
       <c r="D88" t="n">
-        <v>40.2916666666667</v>
+        <v>39.7604166666667</v>
       </c>
       <c r="E88" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F88" t="n">
-        <v>16.6666666666667</v>
+        <v>17.7083333333333</v>
       </c>
     </row>
     <row r="89">
@@ -2135,13 +2135,13 @@
         <v>218</v>
       </c>
       <c r="D89" t="n">
-        <v>39.5321100917431</v>
+        <v>39.2614678899083</v>
       </c>
       <c r="E89" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F89" t="n">
-        <v>11.4678899082569</v>
+        <v>12.3853211009174</v>
       </c>
     </row>
     <row r="90">
@@ -2155,13 +2155,13 @@
         <v>147</v>
       </c>
       <c r="D90" t="n">
-        <v>35.3537414965986</v>
+        <v>34.5918367346939</v>
       </c>
       <c r="E90" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F90" t="n">
-        <v>25.8503401360544</v>
+        <v>27.2108843537415</v>
       </c>
     </row>
     <row r="91">
@@ -2175,13 +2175,13 @@
         <v>88</v>
       </c>
       <c r="D91" t="n">
-        <v>39.125</v>
+        <v>38.8409090909091</v>
       </c>
       <c r="E91" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F91" t="n">
-        <v>30.6818181818182</v>
+        <v>31.8181818181818</v>
       </c>
     </row>
     <row r="92">
@@ -2195,13 +2195,13 @@
         <v>122</v>
       </c>
       <c r="D92" t="n">
-        <v>37.516393442623</v>
+        <v>36.8032786885246</v>
       </c>
       <c r="E92" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F92" t="n">
-        <v>9.8360655737705</v>
+        <v>10.655737704918</v>
       </c>
     </row>
     <row r="93">
@@ -2215,13 +2215,13 @@
         <v>123</v>
       </c>
       <c r="D93" t="n">
-        <v>34.3983739837398</v>
+        <v>33.8211382113821</v>
       </c>
       <c r="E93" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F93" t="n">
-        <v>20.3252032520325</v>
+        <v>23.5772357723577</v>
       </c>
     </row>
     <row r="94">
@@ -2235,13 +2235,13 @@
         <v>151</v>
       </c>
       <c r="D94" t="n">
-        <v>35.5960264900662</v>
+        <v>35.1721854304636</v>
       </c>
       <c r="E94" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F94" t="n">
-        <v>20.5298013245033</v>
+        <v>23.841059602649</v>
       </c>
     </row>
     <row r="95">
@@ -2255,13 +2255,13 @@
         <v>131</v>
       </c>
       <c r="D95" t="n">
-        <v>38.3206106870229</v>
+        <v>37.8167938931298</v>
       </c>
       <c r="E95" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F95" t="n">
-        <v>16.793893129771</v>
+        <v>16.030534351145</v>
       </c>
     </row>
     <row r="96">
@@ -2275,13 +2275,13 @@
         <v>205</v>
       </c>
       <c r="D96" t="n">
-        <v>36.619512195122</v>
+        <v>36.1219512195122</v>
       </c>
       <c r="E96" t="n">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F96" t="n">
-        <v>10.2439024390244</v>
+        <v>13.1707317073171</v>
       </c>
     </row>
     <row r="97">
@@ -2292,16 +2292,16 @@
         <v>18</v>
       </c>
       <c r="C97" t="n">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="D97" t="n">
-        <v>42.2193548387097</v>
+        <v>43.0760233918129</v>
       </c>
       <c r="E97" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="F97" t="n">
-        <v>12.9032258064516</v>
+        <v>12.280701754386</v>
       </c>
     </row>
     <row r="98">
@@ -2312,16 +2312,16 @@
         <v>18</v>
       </c>
       <c r="C98" t="n">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="D98" t="n">
-        <v>42.3464912280702</v>
+        <v>41.7924528301887</v>
       </c>
       <c r="E98" t="n">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="F98" t="n">
-        <v>7.89473684210526</v>
+        <v>8.49056603773585</v>
       </c>
     </row>
     <row r="99">
@@ -2335,13 +2335,13 @@
         <v>252</v>
       </c>
       <c r="D99" t="n">
-        <v>40.75</v>
+        <v>39.5238095238095</v>
       </c>
       <c r="E99" t="n">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="F99" t="n">
-        <v>15.4761904761905</v>
+        <v>19.4444444444444</v>
       </c>
     </row>
     <row r="100">
@@ -2352,16 +2352,16 @@
         <v>18</v>
       </c>
       <c r="C100" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D100" t="n">
-        <v>37.6394557823129</v>
+        <v>35.1301369863014</v>
       </c>
       <c r="E100" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F100" t="n">
-        <v>18.3673469387755</v>
+        <v>30.1369863013699</v>
       </c>
     </row>
     <row r="101">
@@ -2372,16 +2372,16 @@
         <v>18</v>
       </c>
       <c r="C101" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D101" t="n">
-        <v>42.5210526315789</v>
+        <v>41.3874345549738</v>
       </c>
       <c r="E101" t="n">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="F101" t="n">
-        <v>13.1578947368421</v>
+        <v>20.4188481675393</v>
       </c>
     </row>
     <row r="102">
@@ -2395,13 +2395,13 @@
         <v>129</v>
       </c>
       <c r="D102" t="n">
-        <v>41.2248062015504</v>
+        <v>41.0077519379845</v>
       </c>
       <c r="E102" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F102" t="n">
-        <v>15.5038759689922</v>
+        <v>18.6046511627907</v>
       </c>
     </row>
     <row r="103">
@@ -2415,13 +2415,13 @@
         <v>164</v>
       </c>
       <c r="D103" t="n">
-        <v>42.6951219512195</v>
+        <v>41.7926829268293</v>
       </c>
       <c r="E103" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F103" t="n">
-        <v>14.0243902439024</v>
+        <v>16.4634146341463</v>
       </c>
     </row>
     <row r="104">
@@ -2432,16 +2432,16 @@
         <v>18</v>
       </c>
       <c r="C104" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D104" t="n">
-        <v>36.8863636363636</v>
+        <v>37.2921348314607</v>
       </c>
       <c r="E104" t="n">
         <v>78</v>
       </c>
       <c r="F104" t="n">
-        <v>11.3636363636364</v>
+        <v>12.3595505617977</v>
       </c>
     </row>
     <row r="105">
@@ -2452,16 +2452,16 @@
         <v>18</v>
       </c>
       <c r="C105" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D105" t="n">
-        <v>37.6842105263158</v>
+        <v>37.0117647058824</v>
       </c>
       <c r="E105" t="n">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F105" t="n">
-        <v>11.1111111111111</v>
+        <v>15.8823529411765</v>
       </c>
     </row>
     <row r="106">
@@ -2475,13 +2475,13 @@
         <v>172</v>
       </c>
       <c r="D106" t="n">
-        <v>39.0526315789474</v>
+        <v>39.0813953488372</v>
       </c>
       <c r="E106" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F106" t="n">
-        <v>18.0232558139535</v>
+        <v>19.1860465116279</v>
       </c>
     </row>
     <row r="107">
@@ -2492,16 +2492,16 @@
         <v>18</v>
       </c>
       <c r="C107" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D107" t="n">
-        <v>36.1512605042017</v>
+        <v>36.1858407079646</v>
       </c>
       <c r="E107" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F107" t="n">
-        <v>14.2857142857143</v>
+        <v>15.0442477876106</v>
       </c>
     </row>
   </sheetData>
@@ -2738,13 +2738,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36D96DD2-B88A-43D5-A2E4-012FA4E0860C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE843BB9-3561-4578-864C-740E454397B9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2D044EB-FC5D-4C22-8FA8-2BC1A8D0C1EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E7F06F-C5C1-4454-9AA7-D1DF85923C04}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86AB3EF7-48EC-458E-B43E-AB47248920D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8666582-CE71-42CB-B0A8-C4BF12435D6F}"/>
 </file>
--- a/data/ALLE_zeitreihe.xlsx
+++ b/data/ALLE_zeitreihe.xlsx
@@ -398,10 +398,10 @@
         <v>32.9736842105263</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F2" t="n">
-        <v>28.9473684210526</v>
+        <v>18.4210526315789</v>
       </c>
     </row>
     <row r="3">
@@ -418,10 +418,10 @@
         <v>31.983606557377</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F3" t="n">
-        <v>36.8852459016393</v>
+        <v>29.5081967213115</v>
       </c>
     </row>
     <row r="4">
@@ -438,10 +438,10 @@
         <v>33.4949494949495</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>28.2828282828283</v>
+        <v>19.1919191919192</v>
       </c>
     </row>
     <row r="5">
@@ -458,10 +458,10 @@
         <v>32.7079646017699</v>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F5" t="n">
-        <v>24.7787610619469</v>
+        <v>16.8141592920354</v>
       </c>
     </row>
     <row r="6">
@@ -478,10 +478,10 @@
         <v>33.4883720930233</v>
       </c>
       <c r="E6" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F6" t="n">
-        <v>20.9302325581395</v>
+        <v>20.1550387596899</v>
       </c>
     </row>
     <row r="7">
@@ -498,10 +498,10 @@
         <v>33.9462365591398</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F7" t="n">
-        <v>34.4086021505376</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -518,10 +518,10 @@
         <v>33.2597402597403</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F8" t="n">
-        <v>29.8701298701299</v>
+        <v>23.3766233766234</v>
       </c>
     </row>
     <row r="9">
@@ -538,10 +538,10 @@
         <v>31.5</v>
       </c>
       <c r="E9" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
-        <v>25.9615384615385</v>
+        <v>20.1923076923077</v>
       </c>
     </row>
     <row r="10">
@@ -558,10 +558,10 @@
         <v>29.031746031746</v>
       </c>
       <c r="E10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F10" t="n">
-        <v>49.2063492063492</v>
+        <v>46.031746031746</v>
       </c>
     </row>
     <row r="11">
@@ -578,10 +578,10 @@
         <v>30.0116279069767</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F11" t="n">
-        <v>41.8604651162791</v>
+        <v>34.8837209302326</v>
       </c>
     </row>
     <row r="12">
@@ -598,10 +598,10 @@
         <v>31.6862745098039</v>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F12" t="n">
-        <v>36.2745098039216</v>
+        <v>31.3725490196078</v>
       </c>
     </row>
     <row r="13">
@@ -618,10 +618,10 @@
         <v>35.0649350649351</v>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F13" t="n">
-        <v>22.0779220779221</v>
+        <v>19.4805194805195</v>
       </c>
     </row>
     <row r="14">
@@ -638,10 +638,10 @@
         <v>34.6818181818182</v>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F14" t="n">
-        <v>28.7878787878788</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -658,10 +658,10 @@
         <v>31.5689655172414</v>
       </c>
       <c r="E15" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F15" t="n">
-        <v>27.5862068965517</v>
+        <v>24.1379310344828</v>
       </c>
     </row>
     <row r="16">
@@ -678,10 +678,10 @@
         <v>29.1896551724138</v>
       </c>
       <c r="E16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F16" t="n">
-        <v>48.2758620689655</v>
+        <v>44.8275862068966</v>
       </c>
     </row>
     <row r="17">
@@ -698,10 +698,10 @@
         <v>32.8759124087591</v>
       </c>
       <c r="E17" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F17" t="n">
-        <v>23.3576642335766</v>
+        <v>18.978102189781</v>
       </c>
     </row>
     <row r="18">
@@ -718,10 +718,10 @@
         <v>31.5948275862069</v>
       </c>
       <c r="E18" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F18" t="n">
-        <v>20.6896551724138</v>
+        <v>17.2413793103448</v>
       </c>
     </row>
     <row r="19">
@@ -738,10 +738,10 @@
         <v>34.5609756097561</v>
       </c>
       <c r="E19" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19" t="n">
-        <v>35.7723577235772</v>
+        <v>34.9593495934959</v>
       </c>
     </row>
     <row r="20">
@@ -758,10 +758,10 @@
         <v>31.0117647058824</v>
       </c>
       <c r="E20" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F20" t="n">
-        <v>35.2941176470588</v>
+        <v>31.7647058823529</v>
       </c>
     </row>
     <row r="21">
@@ -778,10 +778,10 @@
         <v>29.9347826086956</v>
       </c>
       <c r="E21" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="F21" t="n">
-        <v>47.8260869565217</v>
+        <v>31.8840579710145</v>
       </c>
     </row>
     <row r="22">
@@ -798,10 +798,10 @@
         <v>30.6724137931035</v>
       </c>
       <c r="E22" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F22" t="n">
-        <v>42.2413793103448</v>
+        <v>32.7586206896552</v>
       </c>
     </row>
     <row r="23">
@@ -818,10 +818,10 @@
         <v>31.4220183486239</v>
       </c>
       <c r="E23" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F23" t="n">
-        <v>33.9449541284404</v>
+        <v>22.9357798165138</v>
       </c>
     </row>
     <row r="24">
@@ -838,10 +838,10 @@
         <v>26.4597701149425</v>
       </c>
       <c r="E24" t="n">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="F24" t="n">
-        <v>72.9885057471264</v>
+        <v>47.1264367816092</v>
       </c>
     </row>
     <row r="25">
@@ -858,10 +858,10 @@
         <v>26.3765432098765</v>
       </c>
       <c r="E25" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F25" t="n">
-        <v>57.4074074074074</v>
+        <v>54.9382716049383</v>
       </c>
     </row>
     <row r="26">
@@ -878,10 +878,10 @@
         <v>31.7864077669903</v>
       </c>
       <c r="E26" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F26" t="n">
-        <v>38.8349514563107</v>
+        <v>32.0388349514563</v>
       </c>
     </row>
     <row r="27">
@@ -898,10 +898,10 @@
         <v>29.8897637795276</v>
       </c>
       <c r="E27" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F27" t="n">
-        <v>54.3307086614173</v>
+        <v>47.244094488189</v>
       </c>
     </row>
     <row r="28">
@@ -918,10 +918,10 @@
         <v>30</v>
       </c>
       <c r="E28" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="F28" t="n">
-        <v>56.7307692307692</v>
+        <v>40.3846153846154</v>
       </c>
     </row>
     <row r="29">
@@ -938,10 +938,10 @@
         <v>29.247311827957</v>
       </c>
       <c r="E29" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>52.6881720430108</v>
+        <v>47.3118279569892</v>
       </c>
     </row>
     <row r="30">
@@ -958,10 +958,10 @@
         <v>31.3064516129032</v>
       </c>
       <c r="E30" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F30" t="n">
-        <v>45.1612903225806</v>
+        <v>29.0322580645161</v>
       </c>
     </row>
     <row r="31">
@@ -978,10 +978,10 @@
         <v>31.3515625</v>
       </c>
       <c r="E31" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F31" t="n">
-        <v>35.15625</v>
+        <v>28.90625</v>
       </c>
     </row>
     <row r="32">
@@ -998,10 +998,10 @@
         <v>30.3815789473684</v>
       </c>
       <c r="E32" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F32" t="n">
-        <v>40.7894736842105</v>
+        <v>34.2105263157895</v>
       </c>
     </row>
     <row r="33">
@@ -1018,10 +1018,10 @@
         <v>30.0506329113924</v>
       </c>
       <c r="E33" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F33" t="n">
-        <v>43.0379746835443</v>
+        <v>36.7088607594937</v>
       </c>
     </row>
     <row r="34">
@@ -1038,10 +1038,10 @@
         <v>33.3</v>
       </c>
       <c r="E34" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F34" t="n">
-        <v>35</v>
+        <v>31.6666666666667</v>
       </c>
     </row>
     <row r="35">
@@ -1058,10 +1058,10 @@
         <v>26.7755102040816</v>
       </c>
       <c r="E35" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F35" t="n">
-        <v>67.3469387755102</v>
+        <v>59.1836734693878</v>
       </c>
     </row>
     <row r="36">
@@ -1078,10 +1078,10 @@
         <v>32.685393258427</v>
       </c>
       <c r="E36" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F36" t="n">
-        <v>24.7191011235955</v>
+        <v>22.4719101123596</v>
       </c>
     </row>
     <row r="37">
@@ -1098,10 +1098,10 @@
         <v>33.9724770642202</v>
       </c>
       <c r="E37" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F37" t="n">
-        <v>16.9724770642202</v>
+        <v>19.2660550458716</v>
       </c>
     </row>
     <row r="38">
@@ -1118,10 +1118,10 @@
         <v>42.9311926605505</v>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F38" t="n">
-        <v>15.1376146788991</v>
+        <v>12.3853211009174</v>
       </c>
     </row>
     <row r="39">
@@ -1138,10 +1138,10 @@
         <v>33.0310880829016</v>
       </c>
       <c r="E39" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F39" t="n">
-        <v>25.9067357512953</v>
+        <v>22.7979274611399</v>
       </c>
     </row>
     <row r="40">
@@ -1158,10 +1158,10 @@
         <v>30.2727272727273</v>
       </c>
       <c r="E40" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F40" t="n">
-        <v>44.1558441558442</v>
+        <v>33.7662337662338</v>
       </c>
     </row>
     <row r="41">
@@ -1178,10 +1178,10 @@
         <v>24.0507614213198</v>
       </c>
       <c r="E41" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F41" t="n">
-        <v>77.1573604060914</v>
+        <v>73.0964467005076</v>
       </c>
     </row>
     <row r="42">
@@ -1198,10 +1198,10 @@
         <v>28.0804597701149</v>
       </c>
       <c r="E42" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F42" t="n">
-        <v>58.6206896551724</v>
+        <v>54.0229885057471</v>
       </c>
     </row>
     <row r="43">
@@ -1218,10 +1218,10 @@
         <v>29.5230769230769</v>
       </c>
       <c r="E43" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F43" t="n">
-        <v>49.2307692307692</v>
+        <v>44.6153846153846</v>
       </c>
     </row>
     <row r="44">
@@ -1238,10 +1238,10 @@
         <v>30.2555555555556</v>
       </c>
       <c r="E44" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="F44" t="n">
-        <v>42.2222222222222</v>
+        <v>28.8888888888889</v>
       </c>
     </row>
     <row r="45">
@@ -1258,10 +1258,10 @@
         <v>28.3214285714286</v>
       </c>
       <c r="E45" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F45" t="n">
-        <v>48.2142857142857</v>
+        <v>41.0714285714286</v>
       </c>
     </row>
     <row r="46">
@@ -1278,10 +1278,10 @@
         <v>26.7046979865772</v>
       </c>
       <c r="E46" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F46" t="n">
-        <v>61.0738255033557</v>
+        <v>54.3624161073826</v>
       </c>
     </row>
     <row r="47">
@@ -1298,10 +1298,10 @@
         <v>34.265306122449</v>
       </c>
       <c r="E47" t="n">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="F47" t="n">
-        <v>23.9795918367347</v>
+        <v>18.3673469387755</v>
       </c>
     </row>
     <row r="48">
@@ -1318,10 +1318,10 @@
         <v>29.84375</v>
       </c>
       <c r="E48" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F48" t="n">
-        <v>48.4375</v>
+        <v>45.3125</v>
       </c>
     </row>
     <row r="49">
@@ -1338,10 +1338,10 @@
         <v>29.4285714285714</v>
       </c>
       <c r="E49" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="F49" t="n">
-        <v>62.8571428571429</v>
+        <v>54.2857142857143</v>
       </c>
     </row>
     <row r="50">
@@ -1358,10 +1358,10 @@
         <v>31.0438596491228</v>
       </c>
       <c r="E50" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F50" t="n">
-        <v>32.4561403508772</v>
+        <v>24.5614035087719</v>
       </c>
     </row>
     <row r="51">
@@ -1378,10 +1378,10 @@
         <v>35.0714285714286</v>
       </c>
       <c r="E51" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F51" t="n">
-        <v>27.1428571428572</v>
+        <v>21.4285714285714</v>
       </c>
     </row>
     <row r="52">
@@ -1398,10 +1398,10 @@
         <v>30.6979865771812</v>
       </c>
       <c r="E52" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F52" t="n">
-        <v>14.7651006711409</v>
+        <v>12.751677852349</v>
       </c>
     </row>
     <row r="53">
@@ -1418,10 +1418,10 @@
         <v>29.9714285714286</v>
       </c>
       <c r="E53" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F53" t="n">
-        <v>47.1428571428571</v>
+        <v>34.2857142857143</v>
       </c>
     </row>
     <row r="54">
@@ -1438,10 +1438,10 @@
         <v>28.421052631579</v>
       </c>
       <c r="E54" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>43.421052631579</v>
+        <v>35.5263157894737</v>
       </c>
     </row>
     <row r="55">
@@ -1458,10 +1458,10 @@
         <v>29.2753623188406</v>
       </c>
       <c r="E55" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F55" t="n">
-        <v>52.1739130434783</v>
+        <v>40.5797101449275</v>
       </c>
     </row>
     <row r="56">
@@ -1478,10 +1478,10 @@
         <v>26.0162601626016</v>
       </c>
       <c r="E56" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F56" t="n">
-        <v>63.4146341463415</v>
+        <v>60.1626016260163</v>
       </c>
     </row>
     <row r="57">
@@ -1498,10 +1498,10 @@
         <v>28.6082474226804</v>
       </c>
       <c r="E57" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="F57" t="n">
-        <v>64.9484536082474</v>
+        <v>37.1134020618557</v>
       </c>
     </row>
     <row r="58">
@@ -1518,10 +1518,10 @@
         <v>29.7564102564103</v>
       </c>
       <c r="E58" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="F58" t="n">
-        <v>39.7435897435897</v>
+        <v>20.5128205128205</v>
       </c>
     </row>
     <row r="59">
@@ -1538,10 +1538,10 @@
         <v>30.1014492753623</v>
       </c>
       <c r="E59" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F59" t="n">
-        <v>44.9275362318841</v>
+        <v>37.6811594202899</v>
       </c>
     </row>
     <row r="60">
@@ -1558,10 +1558,10 @@
         <v>32.2424242424242</v>
       </c>
       <c r="E60" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F60" t="n">
-        <v>39.3939393939394</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="61">
@@ -1598,10 +1598,10 @@
         <v>33.3670886075949</v>
       </c>
       <c r="E62" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F62" t="n">
-        <v>40.5063291139241</v>
+        <v>32.9113924050633</v>
       </c>
     </row>
     <row r="63">
@@ -1618,10 +1618,10 @@
         <v>30.9565217391304</v>
       </c>
       <c r="E63" t="n">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="F63" t="n">
-        <v>40.9937888198758</v>
+        <v>33.5403726708074</v>
       </c>
     </row>
     <row r="64">
@@ -1638,10 +1638,10 @@
         <v>30.0126582278481</v>
       </c>
       <c r="E64" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F64" t="n">
-        <v>48.7341772151899</v>
+        <v>41.7721518987342</v>
       </c>
     </row>
     <row r="65">
@@ -1658,10 +1658,10 @@
         <v>31.037037037037</v>
       </c>
       <c r="E65" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F65" t="n">
-        <v>48.1481481481482</v>
+        <v>36.1111111111111</v>
       </c>
     </row>
     <row r="66">
@@ -1678,10 +1678,10 @@
         <v>28.9371428571429</v>
       </c>
       <c r="E66" t="n">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="F66" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67">
@@ -1698,10 +1698,10 @@
         <v>32</v>
       </c>
       <c r="E67" t="n">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="F67" t="n">
-        <v>40.8536585365854</v>
+        <v>27.4390243902439</v>
       </c>
     </row>
     <row r="68">
@@ -1718,10 +1718,10 @@
         <v>29.9484536082474</v>
       </c>
       <c r="E68" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F68" t="n">
-        <v>37.1134020618557</v>
+        <v>27.8350515463918</v>
       </c>
     </row>
     <row r="69">
@@ -1738,10 +1738,10 @@
         <v>34.2302405498282</v>
       </c>
       <c r="E69" t="n">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="F69" t="n">
-        <v>34.3642611683849</v>
+        <v>30.2405498281787</v>
       </c>
     </row>
     <row r="70">
@@ -1758,10 +1758,10 @@
         <v>33.0941704035874</v>
       </c>
       <c r="E70" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="F70" t="n">
-        <v>21.52466367713</v>
+        <v>17.0403587443946</v>
       </c>
     </row>
     <row r="71">
@@ -1778,10 +1778,10 @@
         <v>30.504854368932</v>
       </c>
       <c r="E71" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F71" t="n">
-        <v>38.3495145631068</v>
+        <v>37.378640776699</v>
       </c>
     </row>
     <row r="72">
@@ -1798,10 +1798,10 @@
         <v>36.6421052631579</v>
       </c>
       <c r="E72" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F72" t="n">
-        <v>24.2105263157895</v>
+        <v>18.9473684210526</v>
       </c>
     </row>
     <row r="73">
@@ -1818,10 +1818,10 @@
         <v>34.4087591240876</v>
       </c>
       <c r="E73" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F73" t="n">
-        <v>16.7883211678832</v>
+        <v>10.948905109489</v>
       </c>
     </row>
     <row r="74">
@@ -1838,10 +1838,10 @@
         <v>33.2280701754386</v>
       </c>
       <c r="E74" t="n">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="F74" t="n">
-        <v>40.3508771929825</v>
+        <v>28.6549707602339</v>
       </c>
     </row>
     <row r="75">
@@ -1858,10 +1858,10 @@
         <v>32.4935897435897</v>
       </c>
       <c r="E75" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="F75" t="n">
-        <v>36.5384615384615</v>
+        <v>28.2051282051282</v>
       </c>
     </row>
     <row r="76">
@@ -1878,10 +1878,10 @@
         <v>35.25</v>
       </c>
       <c r="E76" t="n">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F76" t="n">
-        <v>29.9107142857143</v>
+        <v>23.2142857142857</v>
       </c>
     </row>
     <row r="77">
@@ -1898,10 +1898,10 @@
         <v>30.0446096654275</v>
       </c>
       <c r="E77" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F77" t="n">
-        <v>50.185873605948</v>
+        <v>47.2118959107807</v>
       </c>
     </row>
     <row r="78">
@@ -1918,10 +1918,10 @@
         <v>32.2307692307692</v>
       </c>
       <c r="E78" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="F78" t="n">
-        <v>36.2637362637363</v>
+        <v>19.7802197802198</v>
       </c>
     </row>
     <row r="79">
@@ -1938,10 +1938,10 @@
         <v>35.6153846153846</v>
       </c>
       <c r="E79" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F79" t="n">
-        <v>16.4835164835165</v>
+        <v>12.0879120879121</v>
       </c>
     </row>
     <row r="80">
@@ -1958,10 +1958,10 @@
         <v>33.5942028985507</v>
       </c>
       <c r="E80" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F80" t="n">
-        <v>10.1449275362319</v>
+        <v>5.79710144927536</v>
       </c>
     </row>
     <row r="81">
@@ -1978,10 +1978,10 @@
         <v>32.7959183673469</v>
       </c>
       <c r="E81" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F81" t="n">
-        <v>19.047619047619</v>
+        <v>12.2448979591837</v>
       </c>
     </row>
     <row r="82">
@@ -1998,10 +1998,10 @@
         <v>32.0769230769231</v>
       </c>
       <c r="E82" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F82" t="n">
-        <v>35.3846153846154</v>
+        <v>29.2307692307692</v>
       </c>
     </row>
     <row r="83">
@@ -2018,10 +2018,10 @@
         <v>32.7688172043011</v>
       </c>
       <c r="E83" t="n">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="F83" t="n">
-        <v>29.0322580645161</v>
+        <v>18.8172043010753</v>
       </c>
     </row>
     <row r="84">
@@ -2038,10 +2038,10 @@
         <v>36.4179894179894</v>
       </c>
       <c r="E84" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="F84" t="n">
-        <v>23.8095238095238</v>
+        <v>19.047619047619</v>
       </c>
     </row>
     <row r="85">
@@ -2058,10 +2058,10 @@
         <v>36.8272727272727</v>
       </c>
       <c r="E85" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F85" t="n">
-        <v>20.9090909090909</v>
+        <v>12.7272727272727</v>
       </c>
     </row>
     <row r="86">
@@ -2078,10 +2078,10 @@
         <v>37.3065693430657</v>
       </c>
       <c r="E86" t="n">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="F86" t="n">
-        <v>40.1459854014598</v>
+        <v>18.2481751824817</v>
       </c>
     </row>
     <row r="87">
@@ -2098,10 +2098,10 @@
         <v>37.6359649122807</v>
       </c>
       <c r="E87" t="n">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="F87" t="n">
-        <v>34.6491228070175</v>
+        <v>28.0701754385965</v>
       </c>
     </row>
     <row r="88">
@@ -2138,10 +2138,10 @@
         <v>39.2614678899083</v>
       </c>
       <c r="E89" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F89" t="n">
-        <v>12.3853211009174</v>
+        <v>9.63302752293578</v>
       </c>
     </row>
     <row r="90">
@@ -2158,10 +2158,10 @@
         <v>34.5918367346939</v>
       </c>
       <c r="E90" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F90" t="n">
-        <v>27.2108843537415</v>
+        <v>25.8503401360544</v>
       </c>
     </row>
     <row r="91">
@@ -2178,10 +2178,10 @@
         <v>38.8409090909091</v>
       </c>
       <c r="E91" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F91" t="n">
-        <v>31.8181818181818</v>
+        <v>22.7272727272727</v>
       </c>
     </row>
     <row r="92">
@@ -2198,10 +2198,10 @@
         <v>36.8032786885246</v>
       </c>
       <c r="E92" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F92" t="n">
-        <v>10.655737704918</v>
+        <v>7.37704918032787</v>
       </c>
     </row>
     <row r="93">
@@ -2218,10 +2218,10 @@
         <v>33.8211382113821</v>
       </c>
       <c r="E93" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="F93" t="n">
-        <v>23.5772357723577</v>
+        <v>16.260162601626</v>
       </c>
     </row>
     <row r="94">
@@ -2238,10 +2238,10 @@
         <v>35.1721854304636</v>
       </c>
       <c r="E94" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F94" t="n">
-        <v>23.841059602649</v>
+        <v>17.8807947019868</v>
       </c>
     </row>
     <row r="95">
@@ -2258,10 +2258,10 @@
         <v>37.8167938931298</v>
       </c>
       <c r="E95" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F95" t="n">
-        <v>16.030534351145</v>
+        <v>13.7404580152672</v>
       </c>
     </row>
     <row r="96">
@@ -2278,10 +2278,10 @@
         <v>36.1219512195122</v>
       </c>
       <c r="E96" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F96" t="n">
-        <v>13.1707317073171</v>
+        <v>10.7317073170732</v>
       </c>
     </row>
     <row r="97">
@@ -2298,10 +2298,10 @@
         <v>43.0760233918129</v>
       </c>
       <c r="E97" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F97" t="n">
-        <v>12.280701754386</v>
+        <v>9.94152046783626</v>
       </c>
     </row>
     <row r="98">
@@ -2318,10 +2318,10 @@
         <v>41.7924528301887</v>
       </c>
       <c r="E98" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F98" t="n">
-        <v>8.49056603773585</v>
+        <v>5.66037735849056</v>
       </c>
     </row>
     <row r="99">
@@ -2338,10 +2338,10 @@
         <v>39.5238095238095</v>
       </c>
       <c r="E99" t="n">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F99" t="n">
-        <v>19.4444444444444</v>
+        <v>16.6666666666667</v>
       </c>
     </row>
     <row r="100">
@@ -2358,10 +2358,10 @@
         <v>35.1301369863014</v>
       </c>
       <c r="E100" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F100" t="n">
-        <v>30.1369863013699</v>
+        <v>26.7123287671233</v>
       </c>
     </row>
     <row r="101">
@@ -2378,10 +2378,10 @@
         <v>41.3874345549738</v>
       </c>
       <c r="E101" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="F101" t="n">
-        <v>20.4188481675393</v>
+        <v>14.6596858638743</v>
       </c>
     </row>
     <row r="102">
@@ -2398,10 +2398,10 @@
         <v>41.0077519379845</v>
       </c>
       <c r="E102" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F102" t="n">
-        <v>18.6046511627907</v>
+        <v>10.077519379845</v>
       </c>
     </row>
     <row r="103">
@@ -2418,10 +2418,10 @@
         <v>41.7926829268293</v>
       </c>
       <c r="E103" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F103" t="n">
-        <v>16.4634146341463</v>
+        <v>14.0243902439024</v>
       </c>
     </row>
     <row r="104">
@@ -2438,10 +2438,10 @@
         <v>37.2921348314607</v>
       </c>
       <c r="E104" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F104" t="n">
-        <v>12.3595505617977</v>
+        <v>10.1123595505618</v>
       </c>
     </row>
     <row r="105">
@@ -2458,10 +2458,10 @@
         <v>37.0117647058824</v>
       </c>
       <c r="E105" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="F105" t="n">
-        <v>15.8823529411765</v>
+        <v>8.82352941176471</v>
       </c>
     </row>
     <row r="106">
@@ -2478,10 +2478,10 @@
         <v>39.0813953488372</v>
       </c>
       <c r="E106" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F106" t="n">
-        <v>19.1860465116279</v>
+        <v>17.4418604651163</v>
       </c>
     </row>
     <row r="107">
@@ -2498,10 +2498,10 @@
         <v>36.1858407079646</v>
       </c>
       <c r="E107" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F107" t="n">
-        <v>15.0442477876106</v>
+        <v>10.6194690265487</v>
       </c>
     </row>
   </sheetData>
@@ -2738,13 +2738,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE843BB9-3561-4578-864C-740E454397B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C456E3E4-50CB-424A-B3C5-CAC570FEF4F5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E7F06F-C5C1-4454-9AA7-D1DF85923C04}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4944261-7E97-4912-88B8-BF2C9BE03F63}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8666582-CE71-42CB-B0A8-C4BF12435D6F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1B8075A-B42E-4386-90C3-57BBA24B362F}"/>
 </file>